--- a/lab3/график_MPI.xlsx
+++ b/lab3/график_MPI.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\source\repos\parallel programming\lab3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BC3201D-2071-4CA6-93B7-81591FCFD729}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{260CBE2A-D790-42A0-B830-5F8A684489AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8640" yWindow="312" windowWidth="14400" windowHeight="8304" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
